--- a/SGC-CKN/Excel/fe22514d-72b0-4330-a2be-668d0ecfb0af_Lô_CT-02_P14-09_D800_28-03-2026.xlsx
+++ b/SGC-CKN/Excel/fe22514d-72b0-4330-a2be-668d0ecfb0af_Lô_CT-02_P14-09_D800_28-03-2026.xlsx
@@ -1154,7 +1154,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="G11" s="5">
         <v>3.8</v>
@@ -1163,10 +1163,10 @@
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>1.39</v>
+        <v>2.7</v>
       </c>
       <c r="J11" s="8">
-        <v>5.56</v>
+        <v>10.8</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1332,16 +1332,16 @@
         <v>34.5</v>
       </c>
       <c r="G16" s="21">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="H16" s="21">
         <v>0.42</v>
       </c>
       <c r="I16" s="21">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J16" s="8">
-        <v>9.84</v>
+        <v>8.4</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>34</v>
@@ -1364,7 +1364,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="24">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="G17" s="24">
         <v>44</v>
@@ -1373,10 +1373,10 @@
         <v>0.37</v>
       </c>
       <c r="I17" s="24">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J17" s="8">
-        <v>14.73</v>
+        <v>16.36</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>50</v>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="F2" s="5">
         <v>3.8</v>
@@ -1575,10 +1575,10 @@
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>1.39</v>
+        <v>2.7</v>
       </c>
       <c r="I2" s="8">
-        <v>5.56</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1714,16 +1714,16 @@
         <v>34.5</v>
       </c>
       <c r="F7" s="21">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="G7" s="21">
         <v>0.42</v>
       </c>
       <c r="H7" s="21">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I7" s="8">
-        <v>9.84</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>38.6</v>
+        <v>38</v>
       </c>
       <c r="F8" s="24">
         <v>44</v>
@@ -1749,10 +1749,10 @@
         <v>0.37</v>
       </c>
       <c r="H8" s="24">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I8" s="8">
-        <v>14.73</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="F10" s="33">
         <v>49.91</v>
@@ -1807,10 +1807,10 @@
         <v>4.67</v>
       </c>
       <c r="H10" s="33">
-        <v>47.5</v>
+        <v>48.81</v>
       </c>
       <c r="I10" s="33">
-        <v>10.18</v>
+        <v>10.46</v>
       </c>
     </row>
   </sheetData>
